--- a/r4-JoanneumResearch-PreNUDGE-AppData-physical_activity/StructureDefinition-at-prenudge-sitting-hours-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-physical_activity/StructureDefinition-at-prenudge-sitting-hours-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-08T06:51:44+00:00</t>
+    <t>2026-06-25T12:51:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-physical_activity/StructureDefinition-at-prenudge-sitting-hours-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-physical_activity/StructureDefinition-at-prenudge-sitting-hours-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T12:51:02+00:00</t>
+    <t>2026-06-29T13:58:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-physical_activity/StructureDefinition-at-prenudge-sitting-hours-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-physical_activity/StructureDefinition-at-prenudge-sitting-hours-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T13:58:40+00:00</t>
+    <t>2026-06-29T14:49:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-physical_activity/StructureDefinition-at-prenudge-sitting-hours-observation.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-physical_activity/StructureDefinition-at-prenudge-sitting-hours-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T14:49:16+00:00</t>
+    <t>2026-06-29T16:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This FHIR profile defines the Sitting Hours Observation recording the average number of sitting or resting hours per day (excluding sleep). Applicable for both automated wearable measurements (method = Automated) and self-reported values derived from EhisPaqSittingHoursQuestionnaire via SittingHoursQuestionnaireResponseToObservation (method = Manual). Sleep hours must be subtracted by the originating app before recording the value.</t>
+    <t>This FHIR profile defines the Sitting Hours Observation recording the average number of sitting or resting hours per day (excluding sleep). Applicable for both automated wearable measurements (method = Automated) and self-reported values derived from EhisPaqSittingHoursQuestionnaire via SittingHoursQuestionnaireResponseToObservation (method = Manual). Device-derived sitting hours are computed as: Sitting Hours = 24 h − Active Hours − Sleep Hours, where Active Hours (Stehstunden) are hours in which a person has moved at least once (≥ 50 steps per hour). Sleep hours must be subtracted by the originating app before recording the value.</t>
   </si>
   <si>
     <t>Purpose</t>
